--- a/artfynd/A 31491-2026 artfynd.xlsx
+++ b/artfynd/A 31491-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137438528</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -763,6 +763,16 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
@@ -775,7 +785,7 @@
         <v>137438532</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,6 +865,16 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -948,6 +968,16 @@
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -960,7 +990,7 @@
         <v>137438527</v>
       </c>
       <c r="B5" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,6 +1070,16 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -1052,7 +1092,7 @@
         <v>137438529</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,6 +1172,16 @@
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -1144,7 +1194,7 @@
         <v>137438530</v>
       </c>
       <c r="B7" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,6 +1274,16 @@
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>

--- a/artfynd/A 31491-2026 artfynd.xlsx
+++ b/artfynd/A 31491-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137438528</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137438532</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>137438527</v>
       </c>
       <c r="B5" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>137438529</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>137438530</v>
       </c>
       <c r="B7" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31491-2026 artfynd.xlsx
+++ b/artfynd/A 31491-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137438528</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137438532</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137438531</v>
       </c>
       <c r="B4" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>137438527</v>
       </c>
       <c r="B5" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>137438529</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>137438530</v>
       </c>
       <c r="B7" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
